--- a/Analysis/RAG_Ablation/k1_vs_k3_bootstrap_ci.xlsx
+++ b/Analysis/RAG_Ablation/k1_vs_k3_bootstrap_ci.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,50 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>is_pooled_diagnostic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>n_pairs</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mean_tau_k1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>mean_tau_k3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>mean_diff_k1_minus_k3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CI95_lower_percentile</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CI95_upper_percentile</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CI95_lower_bca</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>CI95_upper_bca</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>CI95_contains_zero</t>
         </is>
@@ -474,133 +479,182 @@
           <t>deepseek</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>89</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.173041</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.488745</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-0.315704</v>
       </c>
-      <c r="F2" t="n">
-        <v>-0.47058</v>
-      </c>
       <c r="G2" t="n">
-        <v>-0.159153</v>
+        <v>-0.471328</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.470762</v>
+        <v>-0.160462</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.16084</v>
-      </c>
-      <c r="J2" t="b">
+        <v>-0.473692</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.161945</v>
+      </c>
+      <c r="K2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>90</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.236663</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.187224</v>
+        <v>0.377404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.049439</v>
+        <v>0.38685</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.133343</v>
+        <v>-0.009446</v>
       </c>
       <c r="G3" t="n">
-        <v>0.228507</v>
+        <v>-0.163337</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.133333</v>
+        <v>0.141657</v>
       </c>
       <c r="I3" t="n">
-        <v>0.226269</v>
-      </c>
-      <c r="J3" t="b">
+        <v>-0.164628</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.139618</v>
+      </c>
+      <c r="K3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>89</v>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.305603</v>
+        <v>90</v>
       </c>
       <c r="D4" t="n">
-        <v>0.164416</v>
+        <v>0.236663</v>
       </c>
       <c r="E4" t="n">
-        <v>0.141187</v>
+        <v>0.187224</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.048699</v>
+        <v>0.049439</v>
       </c>
       <c r="G4" t="n">
-        <v>0.329214</v>
+        <v>-0.127591</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.047643</v>
+        <v>0.227591</v>
       </c>
       <c r="I4" t="n">
-        <v>0.333125</v>
-      </c>
-      <c r="J4" t="b">
+        <v>-0.129255</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.226842</v>
+      </c>
+      <c r="K4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Models</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>268</v>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.238429</v>
+        <v>89</v>
       </c>
       <c r="D5" t="n">
-        <v>0.279782</v>
+        <v>0.305603</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.041353</v>
+        <v>0.164416</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.144153</v>
+        <v>0.141187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.063001</v>
+        <v>-0.04701</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.147079</v>
+        <v>0.326188</v>
       </c>
       <c r="I5" t="n">
-        <v>0.061178</v>
-      </c>
-      <c r="J5" t="b">
+        <v>-0.045172</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.327206</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>All Models (pooled diagnostic - do not cite as an estimate)</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>358</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.273367</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.306698</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.033331</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.120154</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.052047</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.119825</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="K6" t="b">
         <v>1</v>
       </c>
     </row>
